--- a/output/graficos_nacionales/plot_nacional_s_fonasa_a_2022.xlsx
+++ b/output/graficos_nacionales/plot_nacional_s_fonasa_a_2022.xlsx
@@ -15497,7 +15497,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Afiliación FONASA</t>
+          <t>Por comunas</t>
         </is>
       </c>
     </row>

--- a/output/graficos_nacionales/plot_nacional_s_fonasa_a_2022.xlsx
+++ b/output/graficos_nacionales/plot_nacional_s_fonasa_a_2022.xlsx
@@ -416,7 +416,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -462,7 +462,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -508,7 +508,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1382,7 +1382,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3958,7 +3958,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -5936,7 +5936,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -5982,7 +5982,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -6304,7 +6304,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -6902,7 +6902,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -6994,7 +6994,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -7500,7 +7500,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -7546,7 +7546,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -7822,7 +7822,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -7960,7 +7960,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -9064,7 +9064,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -9754,7 +9754,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -9892,7 +9892,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -10030,7 +10030,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -10628,7 +10628,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -10674,7 +10674,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -10720,7 +10720,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -10812,7 +10812,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -10858,7 +10858,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -10950,7 +10950,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -10996,7 +10996,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -11042,7 +11042,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -11134,7 +11134,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -11180,7 +11180,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -11226,7 +11226,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -11272,7 +11272,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -11318,7 +11318,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -11410,7 +11410,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -11456,7 +11456,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -11502,7 +11502,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -11594,7 +11594,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -11640,7 +11640,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -11686,7 +11686,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -11732,7 +11732,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -11870,7 +11870,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -11916,7 +11916,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -11962,7 +11962,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -12008,7 +12008,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -12100,7 +12100,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -12192,7 +12192,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -12238,7 +12238,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -12284,7 +12284,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -12330,7 +12330,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -12422,7 +12422,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -12468,7 +12468,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -12514,7 +12514,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -12560,7 +12560,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -12606,7 +12606,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -12652,7 +12652,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -12790,7 +12790,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -12882,7 +12882,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -12928,7 +12928,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -13020,7 +13020,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -13066,7 +13066,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -13204,7 +13204,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -13250,7 +13250,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -13388,7 +13388,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -13434,7 +13434,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -13572,7 +13572,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -13618,7 +13618,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -13802,7 +13802,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -13848,7 +13848,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -13986,7 +13986,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -14032,7 +14032,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -14170,7 +14170,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -14354,7 +14354,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -14400,7 +14400,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -14492,7 +14492,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -14538,7 +14538,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -14676,7 +14676,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -14814,7 +14814,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -14906,7 +14906,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -15136,7 +15136,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -15182,7 +15182,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -15228,7 +15228,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -15320,7 +15320,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -15366,7 +15366,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">

--- a/output/graficos_nacionales/plot_nacional_s_fonasa_a_2022.xlsx
+++ b/output/graficos_nacionales/plot_nacional_s_fonasa_a_2022.xlsx
@@ -2080,7 +2080,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-30 15:52</t>
+    <t xml:space="preserve">2026-08-28 15:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_s_fonasa_a_2022.xlsx
+++ b/output/graficos_nacionales/plot_nacional_s_fonasa_a_2022.xlsx
@@ -2080,7 +2080,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 15:10</t>
+    <t xml:space="preserve">2026-08-29 05:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_s_fonasa_a_2022.xlsx
+++ b/output/graficos_nacionales/plot_nacional_s_fonasa_a_2022.xlsx
@@ -2080,7 +2080,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-29 05:47</t>
+    <t xml:space="preserve">2026-09-07 13:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_s_fonasa_a_2022.xlsx
+++ b/output/graficos_nacionales/plot_nacional_s_fonasa_a_2022.xlsx
@@ -2080,7 +2080,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 13:09</t>
+    <t xml:space="preserve">2026-09-08 10:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
